--- a/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/BEFTA_MASTER_GROUPACCESS.xlsx
+++ b/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/BEFTA_MASTER_GROUPACCESS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39280" yWindow="2120" windowWidth="30200" windowHeight="16620" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39280" yWindow="2120" windowWidth="30200" windowHeight="16620" tabRatio="600" firstSheet="18" activeTab="26" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Jurisdiction" sheetId="1" state="visible" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Arial"/>
       <color indexed="8"/>
@@ -263,6 +263,11 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF000000"/>
+      <sz val="16"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -679,9 +684,6 @@
     <xf numFmtId="49" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -739,6 +741,7 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,6 +754,24 @@
   <dxfs count="339">
     <dxf>
       <font>
+        <name val="Aptos"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
         <name val="Arial"/>
         <family val="2"/>
         <strike val="0"/>
@@ -820,25 +841,6 @@
         <vertAlign val="baseline"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color auto="1"/>
-        <sz val="10"/>
-        <vertAlign val="baseline"/>
-      </font>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -6977,8 +6979,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table9" displayName="Table9" ref="A3:H7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="231" dataDxfId="229" headerRowBorderDxfId="230" tableBorderDxfId="228" totalsRowBorderDxfId="227">
-  <autoFilter ref="A3:H7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table9" displayName="Table9" ref="A3:H5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="231" dataDxfId="229" headerRowBorderDxfId="230" tableBorderDxfId="228" totalsRowBorderDxfId="227">
+  <autoFilter ref="A3:H5"/>
   <tableColumns count="8">
     <tableColumn id="1" name="LiveFrom" dataDxfId="226"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="225"/>
@@ -6994,8 +6996,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table10" displayName="Table10" ref="A3:W11" headerRowCount="1" totalsRowShown="0" headerRowDxfId="218" dataDxfId="216" headerRowBorderDxfId="217" tableBorderDxfId="215" totalsRowBorderDxfId="214">
-  <autoFilter ref="A3:W11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table10" displayName="Table10" ref="A3:W7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="218" dataDxfId="216" headerRowBorderDxfId="217" tableBorderDxfId="215" totalsRowBorderDxfId="214">
+  <autoFilter ref="A3:W7"/>
   <tableColumns count="23">
     <tableColumn id="1" name="LiveFrom" dataDxfId="213"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="212"/>
@@ -7026,8 +7028,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table11" displayName="Table11" ref="A3:V11" headerRowCount="1" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187" totalsRowBorderDxfId="186">
-  <autoFilter ref="A3:V11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table11" displayName="Table11" ref="A3:V7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187" totalsRowBorderDxfId="186">
+  <autoFilter ref="A3:V7"/>
   <tableColumns count="22">
     <tableColumn id="1" name="LiveFrom" dataDxfId="185"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="184"/>
@@ -7057,8 +7059,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table12" displayName="Table12" ref="A3:H11" headerRowCount="1" totalsRowShown="0" headerRowDxfId="163" dataDxfId="161" headerRowBorderDxfId="162" tableBorderDxfId="160" totalsRowBorderDxfId="159">
-  <autoFilter ref="A3:H11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table12" displayName="Table12" ref="A3:H7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="163" dataDxfId="161" headerRowBorderDxfId="162" tableBorderDxfId="160" totalsRowBorderDxfId="159">
+  <autoFilter ref="A3:H7"/>
   <tableColumns count="8">
     <tableColumn id="1" name="LiveFrom" dataDxfId="158"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="157"/>
@@ -7074,8 +7076,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Table25" displayName="Table25" ref="A3:K7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="150" dataDxfId="148" headerRowBorderDxfId="149">
-  <autoFilter ref="A3:K7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Table25" displayName="Table25" ref="A3:K5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="150" dataDxfId="148" headerRowBorderDxfId="149">
+  <autoFilter ref="A3:K5"/>
   <tableColumns count="11">
     <tableColumn id="1" name="LiveFrom" dataDxfId="147" dataCellStyle="Normal 3"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="146" dataCellStyle="Normal 3"/>
@@ -7094,8 +7096,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table14" displayName="Table14" ref="A3:I9" headerRowCount="1" totalsRowShown="0" headerRowDxfId="136" dataDxfId="134" headerRowBorderDxfId="135" tableBorderDxfId="133" totalsRowBorderDxfId="132">
-  <autoFilter ref="A3:I9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table14" displayName="Table14" ref="A3:I6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="136" dataDxfId="134" headerRowBorderDxfId="135" tableBorderDxfId="133" totalsRowBorderDxfId="132">
+  <autoFilter ref="A3:I6"/>
   <tableColumns count="9">
     <tableColumn id="1" name="LiveFrom" dataDxfId="131"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="130"/>
@@ -7112,8 +7114,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table15" displayName="Table15" ref="A3:H11" headerRowCount="1" totalsRowShown="0" headerRowDxfId="122" dataDxfId="120" headerRowBorderDxfId="121" tableBorderDxfId="119" totalsRowBorderDxfId="118">
-  <autoFilter ref="A3:H11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table15" displayName="Table15" ref="A3:H7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="122" dataDxfId="120" headerRowBorderDxfId="121" tableBorderDxfId="119" totalsRowBorderDxfId="118">
+  <autoFilter ref="A3:H7"/>
   <tableColumns count="8">
     <tableColumn id="1" name="LiveFrom" dataDxfId="117"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="116"/>
@@ -7129,8 +7131,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Table16" displayName="Table16" ref="A3:I9" headerRowCount="1" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108" tableBorderDxfId="107" totalsRowBorderDxfId="106">
-  <autoFilter ref="A3:I9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Table16" displayName="Table16" ref="A3:I6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108" tableBorderDxfId="107" totalsRowBorderDxfId="106">
+  <autoFilter ref="A3:I6"/>
   <tableColumns count="9">
     <tableColumn id="1" name="LiveFrom" dataDxfId="105"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="104"/>
@@ -7147,8 +7149,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Table18" displayName="Table18" ref="A3:E9" headerRowCount="1" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
-  <autoFilter ref="A3:E9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Table18" displayName="Table18" ref="A3:E6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
+  <autoFilter ref="A3:E6"/>
   <tableColumns count="5">
     <tableColumn id="1" name="LiveFrom" dataDxfId="91"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="90"/>
@@ -7161,8 +7163,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table3" displayName="Table3" ref="A3:K5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="331" dataDxfId="329" headerRowBorderDxfId="330" tableBorderDxfId="328" totalsRowBorderDxfId="327">
-  <autoFilter ref="A3:K5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table3" displayName="Table3" ref="A3:K4" headerRowCount="1" totalsRowShown="0" headerRowDxfId="331" dataDxfId="329" headerRowBorderDxfId="330" tableBorderDxfId="328" totalsRowBorderDxfId="327">
+  <autoFilter ref="A3:K4"/>
   <tableColumns count="11">
     <tableColumn id="1" name="LiveFrom" dataDxfId="326"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="325"/>
@@ -7181,7 +7183,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Table19" displayName="Table19" ref="A3:F27" headerRowCount="1" totalsRowShown="0" headerRowDxfId="86" dataDxfId="84" headerRowBorderDxfId="85" tableBorderDxfId="83" totalsRowBorderDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Table19" displayName="Table19" ref="A3:F15" headerRowCount="1" totalsRowShown="0" headerRowDxfId="86" dataDxfId="84" headerRowBorderDxfId="85" tableBorderDxfId="83" totalsRowBorderDxfId="82">
   <tableColumns count="6">
     <tableColumn id="1" name="LiveFrom" dataDxfId="81"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="80"/>
@@ -7195,8 +7197,8 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table17" displayName="Table17" ref="A3:F7" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A3:F7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table17" displayName="Table17" ref="A3:F5" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A3:F5"/>
   <tableColumns count="6">
     <tableColumn id="1" name="LiveFrom"/>
     <tableColumn id="2" name="LiveTo"/>
@@ -7210,8 +7212,8 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Table20" displayName="Table20" ref="A3:D7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72" totalsRowBorderDxfId="71">
-  <autoFilter ref="A3:D7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Table20" displayName="Table20" ref="A3:D5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72" totalsRowBorderDxfId="71">
+  <autoFilter ref="A3:D5"/>
   <tableColumns count="4">
     <tableColumn id="1" name="CaseTypeID" dataDxfId="70"/>
     <tableColumn id="2" name="ID" dataDxfId="69" dataCellStyle="Normal 2"/>
@@ -7223,8 +7225,8 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Table21" displayName="Table21" ref="A3:F19" headerRowCount="1" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63" totalsRowBorderDxfId="62">
-  <autoFilter ref="A3:F19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Table21" displayName="Table21" ref="A3:F11" headerRowCount="1" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63" totalsRowBorderDxfId="62">
+  <autoFilter ref="A3:F11"/>
   <tableColumns count="6">
     <tableColumn id="1" name="LiveFrom" dataDxfId="61"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="60"/>
@@ -7238,8 +7240,8 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="Table22" displayName="Table22" ref="A3:F15" headerRowCount="1" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
-  <autoFilter ref="A3:F15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="Table22" displayName="Table22" ref="A3:F9" headerRowCount="1" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+  <autoFilter ref="A3:F9"/>
   <tableColumns count="6">
     <tableColumn id="1" name="LiveFrom" dataDxfId="50"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="49"/>
@@ -7253,8 +7255,8 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table2214" displayName="Table2214" ref="A3:I17" headerRowCount="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
-  <autoFilter ref="A3:I17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table2214" displayName="Table2214" ref="A3:I10" headerRowCount="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
+  <autoFilter ref="A3:I10"/>
   <tableColumns count="9">
     <tableColumn id="1" name="LiveFrom" dataDxfId="39"/>
     <tableColumn id="7" name="LiveTo" dataDxfId="38"/>
@@ -7271,8 +7273,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="Table230" displayName="Table230" ref="A3:K7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
-  <autoFilter ref="A3:K7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="Table230" displayName="Table230" ref="A3:K5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+  <autoFilter ref="A3:K5"/>
   <tableColumns count="11">
     <tableColumn id="1" name="LiveFrom" dataDxfId="25"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="24"/>
@@ -7291,27 +7293,27 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table23031" displayName="Table23031" ref="A3:J9" headerRowCount="1" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="A3:J9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table23031" displayName="Table23031" ref="A3:J6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+  <autoFilter ref="A3:J6"/>
   <tableColumns count="10">
     <tableColumn id="1" name="LiveFrom" dataDxfId="9"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="8"/>
     <tableColumn id="3" name="CaseTypeID" dataDxfId="7"/>
     <tableColumn id="4" name="AccessTypeID" dataDxfId="6"/>
     <tableColumn id="5" name="OrganisationProfileID" dataDxfId="5"/>
-    <tableColumn id="10" name="OrganisationalRoleName" dataDxfId="4"/>
-    <tableColumn id="11" name="GroupRoleName" dataDxfId="3"/>
-    <tableColumn id="12" name="CaseAssignedRoleField" dataDxfId="2"/>
-    <tableColumn id="13" name="GroupAccessEnabled" dataDxfId="1"/>
-    <tableColumn id="24" name="CaseAccessGroupIDTemplate" dataDxfId="0"/>
+    <tableColumn id="10" name="OrganisationalRoleName" dataDxfId="0"/>
+    <tableColumn id="11" name="GroupRoleName" dataDxfId="4"/>
+    <tableColumn id="12" name="CaseAssignedRoleField" dataDxfId="3"/>
+    <tableColumn id="13" name="GroupAccessEnabled" dataDxfId="2"/>
+    <tableColumn id="24" name="CaseAccessGroupIDTemplate" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A3:Q13" headerRowCount="1" totalsRowShown="0" headerRowDxfId="315" dataDxfId="313" headerRowBorderDxfId="314" tableBorderDxfId="312" totalsRowBorderDxfId="311">
-  <autoFilter ref="A3:Q13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A3:Q8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="315" dataDxfId="313" headerRowBorderDxfId="314" tableBorderDxfId="312" totalsRowBorderDxfId="311">
+  <autoFilter ref="A3:Q8"/>
   <tableColumns count="17">
     <tableColumn id="1" name="LiveFrom" dataDxfId="310"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="309"/>
@@ -7352,8 +7354,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table6" displayName="Table6" ref="A3:G13" headerRowCount="1" totalsRowShown="0" headerRowDxfId="293" dataDxfId="291" headerRowBorderDxfId="292" tableBorderDxfId="290" totalsRowBorderDxfId="289" headerRowCellStyle="Normal 2 3">
-  <autoFilter ref="A3:G13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table6" displayName="Table6" ref="A3:G8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="293" dataDxfId="291" headerRowBorderDxfId="292" tableBorderDxfId="290" totalsRowBorderDxfId="289" headerRowCellStyle="Normal 2 3">
+  <autoFilter ref="A3:G8"/>
   <tableColumns count="7">
     <tableColumn id="1" name="LiveFrom" dataDxfId="288"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="287"/>
@@ -7421,8 +7423,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table24" displayName="Table24" ref="A3:J9" headerRowCount="1" totalsRowShown="0" headerRowDxfId="261" dataDxfId="259" headerRowBorderDxfId="260">
-  <autoFilter ref="A3:J9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table24" displayName="Table24" ref="A3:J6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="261" dataDxfId="259" headerRowBorderDxfId="260">
+  <autoFilter ref="A3:J6"/>
   <tableColumns count="10">
     <tableColumn id="1" name="LiveTo" dataDxfId="258"/>
     <tableColumn id="2" name="CaseTypeID" dataDxfId="257"/>
@@ -7440,8 +7442,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table8" displayName="Table8" ref="A3:L13" headerRowCount="1" totalsRowShown="0" headerRowDxfId="248" dataDxfId="246" headerRowBorderDxfId="247" tableBorderDxfId="245" totalsRowBorderDxfId="244">
-  <autoFilter ref="A3:L13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table8" displayName="Table8" ref="A3:L8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="248" dataDxfId="246" headerRowBorderDxfId="247" tableBorderDxfId="245" totalsRowBorderDxfId="244">
+  <autoFilter ref="A3:L8"/>
   <tableColumns count="12">
     <tableColumn id="1" name="LiveFrom" dataDxfId="243"/>
     <tableColumn id="2" name="LiveTo" dataDxfId="242"/>
@@ -8547,8 +8549,8 @@
     <col width="27.33203125" customWidth="1" style="21" min="3" max="3"/>
     <col width="27.1640625" customWidth="1" style="21" min="4" max="4"/>
     <col width="43.83203125" customWidth="1" style="21" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="21" min="6" max="263"/>
-    <col width="8.83203125" customWidth="1" style="21" min="264" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="21" min="6" max="264"/>
+    <col width="8.83203125" customWidth="1" style="21" min="265" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -8574,29 +8576,29 @@
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>Start date from which the data will be valid</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="97" t="inlineStr">
         <is>
           <t>End date until which the data will be valid</t>
         </is>
       </c>
-      <c r="C2" s="99" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>The identifier which defines the casetype code
 MaxLength: 70</t>
         </is>
       </c>
-      <c r="D2" s="99" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>The short description to describe the jurisdiction used on UI display
 MaxLength: 30</t>
         </is>
       </c>
-      <c r="E2" s="99" t="inlineStr">
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>The long description to describe the jurisdiction.
 MaxLength: 100</t>
@@ -8673,8 +8675,8 @@
     <col width="31.6640625" customWidth="1" style="27" min="3" max="4"/>
     <col width="28.33203125" customWidth="1" style="27" min="5" max="6"/>
     <col width="14.33203125" customWidth="1" style="27" min="7" max="7"/>
-    <col width="8.83203125" customWidth="1" style="27" min="8" max="262"/>
-    <col width="8.83203125" customWidth="1" style="27" min="263" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="27" min="8" max="263"/>
+    <col width="8.83203125" customWidth="1" style="27" min="264" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -8700,29 +8702,29 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="99" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>Start date from which the data will be valid</t>
         </is>
       </c>
-      <c r="B2" s="99" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>End date until which the data will be valid</t>
         </is>
       </c>
-      <c r="C2" s="99" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>The unique identifier of the Fixed list
 MaxLength: 40</t>
         </is>
       </c>
-      <c r="D2" s="99" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>The unque ID of an element in the list (ID)
 MaxLength: 40</t>
         </is>
       </c>
-      <c r="E2" s="99" t="inlineStr">
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>The Display name for the list item
 MaxLength: 250</t>
@@ -8760,7 +8762,7 @@
           <t>CategoryID</t>
         </is>
       </c>
-      <c r="G3" s="107" t="inlineStr">
+      <c r="G3" s="106" t="inlineStr">
         <is>
           <t>DisplayOrder</t>
         </is>
@@ -9371,7 +9373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="11.33203125" customWidth="1" min="1" max="1"/>
@@ -9503,7 +9505,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -9526,7 +9528,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -9543,55 +9545,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A6" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Create case</t>
-        </is>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A7" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>CaseUpdated</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Update case</t>
-        </is>
-      </c>
-      <c r="G7" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G26:G28" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G24:G26" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -9617,7 +9573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="15.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9928,7 +9884,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -9976,7 +9932,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -10029,7 +9985,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -10082,7 +10038,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -10124,211 +10080,9 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>createCase</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>Create a case</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>Create a case</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="36" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="Q8" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="R8" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T8" s="37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>updateCase</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>Update with CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>Update a case with CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>CaseUpdated</t>
-        </is>
-      </c>
-      <c r="Q9" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="R9" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T9" s="37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A10" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>updateOrganisation</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>Update organisation</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>Update organisation information</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="I10" s="36" t="inlineStr">
-        <is>
-          <t>CaseUpdated</t>
-        </is>
-      </c>
-      <c r="Q10" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="R10" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V10" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>createOrganisation</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>Create organisation</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Create organisation information</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="Q11" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="R11" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V11" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="G51:G54" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G47:G50" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -10354,7 +10108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="22.6640625" customWidth="1" min="1" max="1"/>
@@ -10614,7 +10368,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -10660,7 +10414,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -10706,7 +10460,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -10752,7 +10506,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -10787,190 +10541,6 @@
         <v>3</v>
       </c>
       <c r="P7" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="35" t="n">
-        <v>42746</v>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>createCase</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="36" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="H8" s="36" t="inlineStr">
-        <is>
-          <t>SingleFormPage</t>
-        </is>
-      </c>
-      <c r="I8" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroup Fields</t>
-        </is>
-      </c>
-      <c r="J8" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>createCase</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
-        <is>
-          <t>SingleFormPageWithComplex</t>
-        </is>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Create organisation</t>
-        </is>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" s="36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A10" s="35" t="n">
-        <v>42746</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>updateCase</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="36" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>SingleFormPage</t>
-        </is>
-      </c>
-      <c r="I10" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroup Fields</t>
-        </is>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>updateCase</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="36" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>SingleFormPageWithComplex</t>
-        </is>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Update organisation</t>
-        </is>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" s="36" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -10999,7 +10569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="28.83203125" customWidth="1" min="1" max="1"/>
@@ -11118,7 +10688,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="37" t="inlineStr">
@@ -11141,7 +10711,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -11169,7 +10739,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -11197,7 +10767,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -11219,116 +10789,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="37" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>CassAccessGroups</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationID</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>Organisation ID</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A10" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>Organisation.OrganisationID</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>Policy Organisation ID</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>OrgPolicyCaseAssignedRole</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Policy Case Assigned Role</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G36 G39 G42 G44:G45" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G32 G35 G38 G40:G41" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -11354,7 +10817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="28.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11445,7 +10908,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
@@ -11481,7 +10944,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">
@@ -11503,76 +10966,9 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A6" s="91" t="n">
-        <v>45247</v>
-      </c>
-      <c r="B6" s="91" t="n">
-        <v>45247</v>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="E6" s="37" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="G6" s="37" t="inlineStr">
-        <is>
-          <t>`Text` orgcases</t>
-        </is>
-      </c>
-      <c r="H6" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t>1:ASC</t>
-        </is>
-      </c>
-      <c r="K6" s="37" t="inlineStr">
-        <is>
-          <t>orgcases</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A7" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="B7" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t>[CASE_REFERENCE]</t>
-        </is>
-      </c>
-      <c r="G7" s="37" t="inlineStr">
-        <is>
-          <t>`CaseReference` orgcases</t>
-        </is>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="37" t="inlineStr">
-        <is>
-          <t>orgcases</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A4:B10" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a date on or after 01/01/2017" type="date" operator="greaterThanOrEqual">
+    <dataValidation sqref="A4:B8" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a date on or after 01/01/2017" type="date" operator="greaterThanOrEqual">
       <formula1>42736</formula1>
     </dataValidation>
   </dataValidations>
@@ -11597,7 +10993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="27.5" customWidth="1" min="1" max="1"/>
@@ -11722,7 +11118,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -11745,7 +11141,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -11768,7 +11164,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -11785,78 +11181,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A7" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G23:G24" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G20:G21" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -11882,7 +11209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="28.83203125" customWidth="1" style="12" min="1" max="1"/>
@@ -11893,8 +11220,8 @@
     <col width="24.1640625" customWidth="1" style="12" min="6" max="6"/>
     <col width="15.33203125" customWidth="1" style="12" min="7" max="7"/>
     <col width="34.33203125" bestFit="1" customWidth="1" style="12" min="8" max="8"/>
-    <col width="8.83203125" customWidth="1" style="12" min="9" max="22"/>
-    <col width="8.83203125" customWidth="1" style="12" min="23" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="12" min="9" max="23"/>
+    <col width="8.83203125" customWidth="1" style="12" min="24" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -12002,7 +11329,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -12025,7 +11352,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -12053,7 +11380,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -12081,7 +11408,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -12103,116 +11430,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A8" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationID</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Organisation ID</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A10" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>Organisation.OrganisationID</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Policy Organisation ID</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>OrgPolicyCaseAssignedRole</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Policy Case Assigned Role</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G37 G40 G43 G45:G46" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G33 G36 G39 G41:G42" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -12238,7 +11458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="27.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12363,7 +11583,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -12386,7 +11606,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -12409,7 +11629,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -12426,78 +11646,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A7" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="G42:G43" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G39:G40" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -12523,7 +11674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="30.83203125" customWidth="1" min="1" max="1"/>
@@ -12617,9 +11768,9 @@
       <c r="A4" s="35" t="n">
         <v>42736</v>
       </c>
-      <c r="C4" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="37" t="inlineStr">
@@ -12637,9 +11788,9 @@
       <c r="A5" s="35" t="n">
         <v>42736</v>
       </c>
-      <c r="C5" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
+      <c r="C5" s="94" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="90" t="inlineStr">
@@ -12657,9 +11808,9 @@
       <c r="A6" s="35" t="n">
         <v>42736</v>
       </c>
-      <c r="C6" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="37" t="inlineStr">
@@ -12668,66 +11819,6 @@
         </is>
       </c>
       <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A7" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C7" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C8" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
@@ -12756,7 +11847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="14.83203125" customWidth="1" min="1" max="1"/>
@@ -12789,7 +11880,7 @@
           <t>PrimaryAndForeignKey Orange</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>ForeignKey Brown</t>
         </is>
@@ -12923,14 +12014,14 @@
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
           <t>FT_CaseAccessGroups</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
-        </is>
-      </c>
       <c r="E4" s="87" t="inlineStr">
         <is>
           <t>Case Type for testing CaseGroupAccess's</t>
@@ -12942,36 +12033,6 @@
         </is>
       </c>
       <c r="I4" s="88" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A5" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C5" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D5" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="E5" s="87" t="inlineStr">
-        <is>
-          <t>Case Type for testing CaseGroupAccess's</t>
-        </is>
-      </c>
-      <c r="F5" s="87" t="inlineStr">
-        <is>
-          <t>BEFTA_MASTER</t>
-        </is>
-      </c>
-      <c r="I5" s="88" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
@@ -13000,7 +12061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -13108,7 +12169,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -13133,7 +12194,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -13158,7 +12219,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -13183,7 +12244,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -13208,7 +12269,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D8" s="36" t="inlineStr">
@@ -13233,7 +12294,7 @@
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
@@ -13258,7 +12319,7 @@
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D10" s="36" t="inlineStr">
@@ -13283,7 +12344,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
@@ -13308,7 +12369,7 @@
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D12" s="36" t="inlineStr">
@@ -13333,7 +12394,7 @@
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D13" s="36" t="inlineStr">
@@ -13358,7 +12419,7 @@
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D14" s="36" t="inlineStr">
@@ -13383,7 +12444,7 @@
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D15" s="36" t="inlineStr">
@@ -13397,306 +12458,6 @@
         </is>
       </c>
       <c r="F15" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A16" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="E16" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A17" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A18" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E18" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A19" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequestField</t>
-        </is>
-      </c>
-      <c r="E19" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F19" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A20" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C20" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D20" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="E20" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F20" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A21" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C21" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D21" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E21" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F21" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A22" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C22" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D22" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E22" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F22" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A23" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C23" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D23" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequestField</t>
-        </is>
-      </c>
-      <c r="E23" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F23" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A24" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C24" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D24" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="E24" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F24" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A25" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C25" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E25" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F25" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A26" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C26" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E26" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F26" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A27" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C27" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D27" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequestField</t>
-        </is>
-      </c>
-      <c r="E27" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
@@ -13725,7 +12486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="34.33203125" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
@@ -13734,8 +12495,8 @@
     <col width="28.5" customWidth="1" style="27" min="4" max="4"/>
     <col width="26.83203125" customWidth="1" style="27" min="5" max="5"/>
     <col width="22.83203125" customWidth="1" style="27" min="6" max="6"/>
-    <col width="8.83203125" customWidth="1" style="27" min="7" max="256"/>
-    <col width="8.83203125" customWidth="1" style="27" min="257" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="27" min="7" max="257"/>
+    <col width="8.83203125" customWidth="1" style="27" min="258" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -13759,11 +12520,11 @@
           <t>ForeignKey Brown</t>
         </is>
       </c>
-      <c r="E1" s="108" t="n"/>
-      <c r="F1" s="108" t="n"/>
+      <c r="E1" s="107" t="n"/>
+      <c r="F1" s="107" t="n"/>
     </row>
     <row r="2" ht="35" customHeight="1">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="108" t="inlineStr">
         <is>
           <t>Start date from which the data will be valid</t>
         </is>
@@ -13773,7 +12534,7 @@
           <t>End date until which the data will be valid</t>
         </is>
       </c>
-      <c r="C2" s="110" t="n"/>
+      <c r="C2" s="109" t="n"/>
       <c r="D2" s="62" t="inlineStr">
         <is>
           <t>Must match ID from Jurisdiction Tab
@@ -13832,7 +12593,7 @@
       <c r="B4" s="35" t="n">
         <v>42736</v>
       </c>
-      <c r="C4" s="111" t="inlineStr">
+      <c r="C4" s="110" t="inlineStr">
         <is>
           <t>master.caseworker@gmail.com</t>
         </is>
@@ -13844,7 +12605,7 @@
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F4" s="36" t="inlineStr">
@@ -13860,7 +12621,7 @@
       <c r="B5" s="35" t="n">
         <v>42736</v>
       </c>
-      <c r="C5" s="111" t="inlineStr">
+      <c r="C5" s="110" t="inlineStr">
         <is>
           <t>master.solicitor.1@gmail.com</t>
         </is>
@@ -13872,66 +12633,10 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F5" s="36" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="B6" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C6" s="111" t="inlineStr">
-        <is>
-          <t>master.caseworker@gmail.com</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>BEFTA_MASTER</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="B7" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C7" s="111" t="inlineStr">
-        <is>
-          <t>master.solicitor.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>BEFTA_MASTER</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>CaseCreated</t>
         </is>
@@ -13941,13 +12646,11 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511806" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13958,7 +12661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="28.83203125" customWidth="1" min="1" max="4"/>
@@ -14032,12 +12735,12 @@
       </c>
     </row>
     <row r="4" ht="20" customFormat="1" customHeight="1" s="86">
-      <c r="A4" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>[Claimant]</t>
         </is>
@@ -14054,12 +12757,12 @@
       </c>
     </row>
     <row r="5" ht="20" customFormat="1" customHeight="1" s="86">
-      <c r="A5" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>[Defendant]</t>
         </is>
@@ -14070,50 +12773,6 @@
         </is>
       </c>
       <c r="D5" s="37" t="inlineStr">
-        <is>
-          <t>The defending party</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customFormat="1" customHeight="1" s="86">
-      <c r="A6" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>[Claimant]</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>Claimant</t>
-        </is>
-      </c>
-      <c r="D6" s="37" t="inlineStr">
-        <is>
-          <t>The person created the case</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="86">
-      <c r="A7" s="95" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>[Defendant]</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>Defendant</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>The defending party</t>
         </is>
@@ -14141,7 +12800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="27.1640625" customWidth="1" min="1" max="1"/>
@@ -14248,7 +12907,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -14273,7 +12932,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -14298,7 +12957,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -14323,7 +12982,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -14348,7 +13007,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D8" s="36" t="inlineStr">
@@ -14373,7 +13032,7 @@
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
@@ -14398,7 +13057,7 @@
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D10" s="36" t="inlineStr">
@@ -14406,7 +13065,7 @@
           <t>createCase</t>
         </is>
       </c>
-      <c r="E10" s="94" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>citizen</t>
         </is>
@@ -14423,7 +13082,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
@@ -14431,212 +13090,12 @@
           <t>updateCase</t>
         </is>
       </c>
-      <c r="E11" s="94" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>citizen</t>
         </is>
       </c>
       <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A12" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>createCase</t>
-        </is>
-      </c>
-      <c r="E12" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A13" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>updateCase</t>
-        </is>
-      </c>
-      <c r="E13" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A14" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D14" s="36" t="inlineStr">
-        <is>
-          <t>createCase</t>
-        </is>
-      </c>
-      <c r="E14" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A15" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D15" s="36" t="inlineStr">
-        <is>
-          <t>updateCase</t>
-        </is>
-      </c>
-      <c r="E15" s="90" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F15" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A16" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="inlineStr">
-        <is>
-          <t>updateOrganisation</t>
-        </is>
-      </c>
-      <c r="E16" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A17" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="inlineStr">
-        <is>
-          <t>createOrganisation</t>
-        </is>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A18" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>createCase</t>
-        </is>
-      </c>
-      <c r="E18" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A19" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="inlineStr">
-        <is>
-          <t>updateCase</t>
-        </is>
-      </c>
-      <c r="E19" s="37" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
@@ -14665,7 +13124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="31.5" customWidth="1" min="1" max="1"/>
@@ -14772,7 +13231,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -14797,7 +13256,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -14822,7 +13281,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -14847,7 +13306,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -14872,7 +13331,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -14897,7 +13356,7 @@
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -14911,156 +13370,6 @@
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A10" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="E10" s="81" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A11" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>CaseUpdated</t>
-        </is>
-      </c>
-      <c r="E11" s="81" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A12" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="E12" s="81" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A13" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>CaseUpdated</t>
-        </is>
-      </c>
-      <c r="E13" s="81" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A14" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>CaseCreated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customFormat="1" customHeight="1" s="14">
-      <c r="A15" s="21" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>CaseUpdated</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
@@ -15089,7 +13398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="25.33203125" customWidth="1" min="1" max="1"/>
@@ -15119,7 +13428,7 @@
           <t>PrimaryAndForeignKey Orange</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>ForeignKey Brown</t>
         </is>
@@ -15225,7 +13534,7 @@
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F4" s="36" t="inlineStr">
@@ -15255,7 +13564,7 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F5" s="36" t="inlineStr">
@@ -15285,7 +13594,7 @@
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F6" s="36" t="inlineStr">
@@ -15315,7 +13624,7 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F7" s="36" t="inlineStr">
@@ -15345,7 +13654,7 @@
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
@@ -15375,7 +13684,7 @@
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
@@ -15405,7 +13714,7 @@
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="F10" s="36" t="inlineStr">
@@ -15419,216 +13728,6 @@
         </is>
       </c>
       <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="37" t="inlineStr">
-        <is>
-          <t>GroupRole1</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A12" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>GroupRole2</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A13" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C13" s="37" t="inlineStr">
-        <is>
-          <t>idam:caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>caseworker-befta_jurisdiction_1</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A14" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>idam:caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="G14" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A15" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>[Claimant]</t>
-        </is>
-      </c>
-      <c r="E15" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>[Claimant]</t>
-        </is>
-      </c>
-      <c r="G15" s="36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H15" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A16" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>[Defendant]</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F16" s="37" t="inlineStr">
-        <is>
-          <t>[Defendant]</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H16" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A17" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C17" s="37" t="inlineStr">
-        <is>
-          <t>idam:citizen</t>
-        </is>
-      </c>
-      <c r="E17" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>citizen</t>
-        </is>
-      </c>
-      <c r="G17" s="36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -15656,7 +13755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col width="21.6640625" customWidth="1" min="1" max="1"/>
@@ -15687,7 +13786,7 @@
           <t>PrimaryAndForeignKey Orange</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>ForeignKey Brown</t>
         </is>
@@ -15734,7 +13833,7 @@
 (YesOrNo field Optional)</t>
         </is>
       </c>
-      <c r="H2" s="96" t="inlineStr">
+      <c r="H2" s="95" t="inlineStr">
         <is>
           <t>Field that Indicates whether this access type is displayed to the user in the Invite User / Edit User UI.
 (YesOrNo field Optional)</t>
@@ -15821,12 +13920,12 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
-          <t>BEFTA_SOLICITOR_1</t>
+          <t>GA_SOLICITOR</t>
         </is>
       </c>
       <c r="E4" s="36" t="inlineStr">
@@ -15869,17 +13968,17 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>BEFTA_SOLICITOR_2</t>
+          <t>GA_OGD</t>
         </is>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>OGD_DWP_PROFILE</t>
+          <t>GOVERNMENT_ORGANISATION_PROFILE</t>
         </is>
       </c>
       <c r="F5" s="36" t="inlineStr">
@@ -15908,102 +14007,6 @@
         </is>
       </c>
       <c r="K5" s="37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="n">
-        <v>44927</v>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>GA_SOLICITOR</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>groupaccesstest_solicitor</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" s="36" t="inlineStr">
-        <is>
-          <t>BEFTA bulk Solicitor Respondent for Org description</t>
-        </is>
-      </c>
-      <c r="J6" s="37" t="inlineStr">
-        <is>
-          <t>BEFTA bulk Solicitor Respondent for Org hint</t>
-        </is>
-      </c>
-      <c r="K6" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="n">
-        <v>44927</v>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>GA_OGD</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>groupaccesstest_ogd</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>BEFTA bulk Solicitor Respondent for Org description2</t>
-        </is>
-      </c>
-      <c r="J7" s="37" t="inlineStr">
-        <is>
-          <t>BEFTA bulk Solicitor Respondent for Org hint2</t>
-        </is>
-      </c>
-      <c r="K7" s="37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16021,7 +14024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col width="21.6640625" customWidth="1" min="1" max="1"/>
@@ -16029,8 +14032,8 @@
     <col width="24.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="26.1640625" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="21.33203125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="27.1640625" customWidth="1" min="6" max="6"/>
-    <col width="18.83203125" customWidth="1" min="7" max="7"/>
+    <col width="50.1640625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="33.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
     <col width="28.83203125" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="28.5" bestFit="1" customWidth="1" min="10" max="10"/>
@@ -16052,7 +14055,7 @@
           <t>PrimaryAndForeignKey Orange</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>ForeignKey Brown</t>
         </is>
@@ -16105,13 +14108,13 @@
 MaxLength: 70</t>
         </is>
       </c>
-      <c r="I2" s="96" t="inlineStr">
+      <c r="I2" s="95" t="inlineStr">
         <is>
           <t>Indicates whether this record is active for group access.
 (YesOrNo field Optional)</t>
         </is>
       </c>
-      <c r="J2" s="96" t="inlineStr">
+      <c r="J2" s="95" t="inlineStr">
         <is>
           <t>A text template used to generate the case access group identifier for role assignments and case data.
 MaxLength: 200</t>
@@ -16170,18 +14173,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="35" t="n">
         <v>44927</v>
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
-          <t>BEFTA_SOLICITOR_1</t>
+          <t>GA_SOLICITOR</t>
         </is>
       </c>
       <c r="E4" s="36" t="inlineStr">
@@ -16189,14 +14192,14 @@
           <t>SOLICITOR_PROFILE</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
-        <is>
-          <t>Role1</t>
+      <c r="F4" s="115" t="inlineStr">
+        <is>
+          <t>CaseProfessionalGroupAccess_Org_Role</t>
         </is>
       </c>
       <c r="G4" s="36" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>CaseProfessionalGroupAccess_GA_Role</t>
         </is>
       </c>
       <c r="H4" s="37" t="inlineStr">
@@ -16215,33 +14218,33 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="35" t="n">
         <v>44927</v>
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>BEFTA_SOLICITOR_2</t>
+          <t>GA_OGD</t>
         </is>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>OGD_DWP_PROFILE</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="inlineStr">
-        <is>
-          <t>Role1</t>
+          <t>GOVERNMENT_ORGANISATION_PROFILE</t>
+        </is>
+      </c>
+      <c r="F5" s="115" t="inlineStr">
+        <is>
+          <t>CaseProfessionalGroupAccess_Org_Role</t>
         </is>
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>CaseProfessionalGroupAccess_GA_Role</t>
         </is>
       </c>
       <c r="H5" s="37" t="inlineStr">
@@ -16260,28 +14263,28 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="35" t="n">
         <v>44927</v>
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
-          <t>BEFTA_SOLICITOR_2</t>
+          <t>GA_OGD</t>
         </is>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>OGD_DWP_PROFILE</t>
-        </is>
-      </c>
-      <c r="F6" s="37" t="inlineStr">
-        <is>
-          <t>Role1</t>
+          <t>GOVERNMENT_ORGANISATION_PROFILE</t>
+        </is>
+      </c>
+      <c r="F6" s="115" t="inlineStr">
+        <is>
+          <t>CaseProfessionalGroupAccess_Org_Role</t>
         </is>
       </c>
       <c r="H6" s="37" t="inlineStr">
@@ -16290,131 +14293,6 @@
         </is>
       </c>
       <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="n">
-        <v>44927</v>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>GA_SOLICITOR</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>groupaccesstest_solicitor</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="G7" s="36" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="H7" s="37" t="inlineStr">
-        <is>
-          <t>GroupRole1</t>
-        </is>
-      </c>
-      <c r="I7" s="37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" s="37" t="inlineStr">
-        <is>
-          <t>BEFTA_MASTER:$ORGID$</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="n">
-        <v>44927</v>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>GA_OGD</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>groupaccesstest_ogd</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="G8" s="36" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>GroupRole1</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" s="37" t="inlineStr">
-        <is>
-          <t>BEFTA_MASTER:$ORGID$</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="n">
-        <v>44927</v>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>GA_OGD</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>groupaccesstest_ogd</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="H9" s="37" t="inlineStr">
-        <is>
-          <t>GroupRole2</t>
-        </is>
-      </c>
-      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16434,7 +14312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="14.5" customWidth="1" min="1" max="1"/>
@@ -16471,7 +14349,7 @@
           <t>PrimaryAndForeignKey Orange</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>ForeignKey Brown</t>
         </is>
@@ -16647,7 +14525,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -16682,7 +14560,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -16717,7 +14595,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -16752,7 +14630,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -16787,7 +14665,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D8" s="36" t="inlineStr">
@@ -16811,181 +14689,6 @@
         </is>
       </c>
       <c r="N8" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="K9" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="N9" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A10" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>Organisation Field 1</t>
-        </is>
-      </c>
-      <c r="G10" s="36" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="K10" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="N10" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>Organisation Policy Field 1</t>
-        </is>
-      </c>
-      <c r="G11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicy</t>
-        </is>
-      </c>
-      <c r="K11" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="N11" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A12" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequestField</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>Change Organisation Request</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequest</t>
-        </is>
-      </c>
-      <c r="K12" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="N12" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A13" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>CaseHistory</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="G13" s="36" t="inlineStr">
-        <is>
-          <t>CaseHistoryViewer</t>
-        </is>
-      </c>
-      <c r="K13" s="36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="N13" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -16993,8 +14696,8 @@
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="B145" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a value that after LiveFrom date" type="custom">
-      <formula1>IF((DATEDIF(A145,B145,"d")&gt;0),B145)</formula1>
+    <dataValidation sqref="B140" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a value that after LiveFrom date" type="custom">
+      <formula1>IF((DATEDIF(A140,B140,"d")&gt;0),B140)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511806" footer="0.3"/>
@@ -17029,8 +14732,8 @@
     <col width="18.5" bestFit="1" customWidth="1" style="27" min="5" max="5"/>
     <col width="14.5" bestFit="1" customWidth="1" style="27" min="6" max="6"/>
     <col width="18" bestFit="1" customWidth="1" style="27" min="7" max="7"/>
-    <col width="11.5" customWidth="1" style="27" min="8" max="14"/>
-    <col width="11.5" customWidth="1" style="27" min="15" max="16384"/>
+    <col width="11.5" customWidth="1" style="27" min="8" max="15"/>
+    <col width="11.5" customWidth="1" style="27" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -17039,7 +14742,7 @@
           <t>Categories</t>
         </is>
       </c>
-      <c r="B1" s="112" t="n"/>
+      <c r="B1" s="111" t="n"/>
       <c r="C1" s="11" t="n"/>
       <c r="D1" s="12" t="n"/>
       <c r="E1" s="12" t="n"/>
@@ -17074,7 +14777,7 @@
           <t>LiveFrom</t>
         </is>
       </c>
-      <c r="B3" s="113" t="inlineStr">
+      <c r="B3" s="112" t="inlineStr">
         <is>
           <t>LiveTo</t>
         </is>
@@ -17106,13 +14809,13 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="114" t="n"/>
-      <c r="B4" s="114" t="n"/>
-      <c r="C4" s="115" t="n"/>
-      <c r="D4" s="115" t="n"/>
-      <c r="E4" s="115" t="n"/>
-      <c r="F4" s="115" t="n"/>
-      <c r="G4" s="115" t="n"/>
+      <c r="A4" s="113" t="n"/>
+      <c r="B4" s="113" t="n"/>
+      <c r="C4" s="114" t="n"/>
+      <c r="D4" s="114" t="n"/>
+      <c r="E4" s="114" t="n"/>
+      <c r="F4" s="114" t="n"/>
+      <c r="G4" s="114" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17128,7 +14831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="33.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -17237,7 +14940,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -17267,7 +14970,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -17297,7 +15000,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -17327,7 +15030,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -17357,7 +15060,7 @@
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D8" s="36" t="inlineStr">
@@ -17376,156 +15079,6 @@
         </is>
       </c>
       <c r="G8" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>OrgPolicyCaseAssignedRole</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A10" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>OrgPolicyReference</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="G10" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="G11" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A12" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>Organisation.OrganisationID</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A13" s="91" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>Organisation.OrganisationName</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>caseworker-befta_master</t>
-        </is>
-      </c>
-      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
@@ -17590,7 +15143,7 @@
           <t>PrimaryAndForeignKey Orange</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>ForeignKey Brown</t>
         </is>
@@ -17724,9 +15277,9 @@
       <c r="A4" s="91" t="n">
         <v>43101</v>
       </c>
-      <c r="C4" s="58" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -17757,9 +15310,9 @@
       <c r="A5" s="91" t="n">
         <v>43101</v>
       </c>
-      <c r="C5" s="58" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups</t>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -17828,8 +15381,8 @@
     <col width="64.6640625" bestFit="1" customWidth="1" style="27" min="15" max="15"/>
     <col width="8.83203125" customWidth="1" style="27" min="16" max="18"/>
     <col width="10.5" customWidth="1" style="27" min="19" max="19"/>
-    <col width="8.83203125" customWidth="1" style="27" min="20" max="261"/>
-    <col width="8.83203125" customWidth="1" style="27" min="262" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="27" min="20" max="262"/>
+    <col width="8.83203125" customWidth="1" style="27" min="263" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -20482,90 +18035,90 @@
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="100" t="n">
+      <c r="A79" s="99" t="n">
         <v>42745</v>
       </c>
-      <c r="C79" s="101" t="inlineStr">
+      <c r="C79" s="100" t="inlineStr">
         <is>
           <t>RespondentComplex</t>
         </is>
       </c>
-      <c r="D79" s="101" t="inlineStr">
+      <c r="D79" s="100" t="inlineStr">
         <is>
           <t>RespAddress3</t>
         </is>
       </c>
-      <c r="E79" s="101" t="inlineStr">
+      <c r="E79" s="100" t="inlineStr">
         <is>
           <t>AddressUK</t>
         </is>
       </c>
-      <c r="H79" s="101" t="inlineStr">
+      <c r="H79" s="100" t="inlineStr">
         <is>
           <t>Respondent address 3</t>
         </is>
       </c>
-      <c r="M79" s="101" t="inlineStr">
+      <c r="M79" s="100" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="100" t="n">
+      <c r="A80" s="99" t="n">
         <v>42745</v>
       </c>
-      <c r="C80" s="101" t="inlineStr">
+      <c r="C80" s="100" t="inlineStr">
         <is>
           <t>RespondentComplex</t>
         </is>
       </c>
-      <c r="D80" s="101" t="inlineStr">
+      <c r="D80" s="100" t="inlineStr">
         <is>
           <t>RespName</t>
         </is>
       </c>
-      <c r="E80" s="101" t="inlineStr">
+      <c r="E80" s="100" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="H80" s="101" t="inlineStr">
+      <c r="H80" s="100" t="inlineStr">
         <is>
           <t>Respondent name</t>
         </is>
       </c>
-      <c r="M80" s="101" t="inlineStr">
+      <c r="M80" s="100" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="100" t="n">
+      <c r="A81" s="99" t="n">
         <v>42745</v>
       </c>
-      <c r="C81" s="101" t="inlineStr">
+      <c r="C81" s="100" t="inlineStr">
         <is>
           <t>RespondentComplex</t>
         </is>
       </c>
-      <c r="D81" s="101" t="inlineStr">
+      <c r="D81" s="100" t="inlineStr">
         <is>
           <t>RespAddress4</t>
         </is>
       </c>
-      <c r="E81" s="101" t="inlineStr">
+      <c r="E81" s="100" t="inlineStr">
         <is>
           <t>AddressUK</t>
         </is>
       </c>
-      <c r="H81" s="101" t="inlineStr">
+      <c r="H81" s="100" t="inlineStr">
         <is>
           <t>Respondent address 4</t>
         </is>
       </c>
-      <c r="M81" s="101" t="inlineStr">
+      <c r="M81" s="100" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
@@ -20817,155 +18370,155 @@
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="102" t="n">
+      <c r="A89" s="101" t="n">
         <v>42736</v>
       </c>
-      <c r="C89" s="103" t="inlineStr">
+      <c r="C89" s="102" t="inlineStr">
         <is>
           <t>DynamicListsComplex</t>
         </is>
       </c>
-      <c r="D89" s="103" t="inlineStr">
+      <c r="D89" s="102" t="inlineStr">
         <is>
           <t>DynamicRadioListComplex</t>
         </is>
       </c>
-      <c r="E89" s="103" t="inlineStr">
+      <c r="E89" s="102" t="inlineStr">
         <is>
           <t>DynamicRadioList</t>
         </is>
       </c>
-      <c r="H89" s="103" t="inlineStr">
+      <c r="H89" s="102" t="inlineStr">
         <is>
           <t>Dynamic Radio List complex</t>
         </is>
       </c>
-      <c r="M89" s="103" t="inlineStr">
+      <c r="M89" s="102" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="102" t="n">
+      <c r="A90" s="101" t="n">
         <v>42736</v>
       </c>
-      <c r="C90" s="103" t="inlineStr">
+      <c r="C90" s="102" t="inlineStr">
         <is>
           <t>DynamicListsComplex</t>
         </is>
       </c>
-      <c r="D90" s="103" t="inlineStr">
+      <c r="D90" s="102" t="inlineStr">
         <is>
           <t>DynamicMultiSelectComplex</t>
         </is>
       </c>
-      <c r="E90" s="103" t="inlineStr">
+      <c r="E90" s="102" t="inlineStr">
         <is>
           <t>DynamicMultiSelectList</t>
         </is>
       </c>
-      <c r="H90" s="103" t="inlineStr">
+      <c r="H90" s="102" t="inlineStr">
         <is>
           <t>Dynamic Radio List complex</t>
         </is>
       </c>
-      <c r="M90" s="103" t="inlineStr">
+      <c r="M90" s="102" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="100" t="n">
+      <c r="A91" s="99" t="n">
         <v>42745</v>
       </c>
-      <c r="C91" s="101" t="inlineStr">
+      <c r="C91" s="100" t="inlineStr">
         <is>
           <t>RespondentComplex6</t>
         </is>
       </c>
-      <c r="D91" s="101" t="inlineStr">
+      <c r="D91" s="100" t="inlineStr">
         <is>
           <t>RespAddress3</t>
         </is>
       </c>
-      <c r="E91" s="101" t="inlineStr">
+      <c r="E91" s="100" t="inlineStr">
         <is>
           <t>AddressUK</t>
         </is>
       </c>
-      <c r="H91" s="101" t="inlineStr">
+      <c r="H91" s="100" t="inlineStr">
         <is>
           <t>Respondent address 3</t>
         </is>
       </c>
-      <c r="M91" s="101" t="inlineStr">
+      <c r="M91" s="100" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="100" t="n">
+      <c r="A92" s="99" t="n">
         <v>42745</v>
       </c>
-      <c r="C92" s="101" t="inlineStr">
+      <c r="C92" s="100" t="inlineStr">
         <is>
           <t>RespondentComplex6</t>
         </is>
       </c>
-      <c r="D92" s="101" t="inlineStr">
+      <c r="D92" s="100" t="inlineStr">
         <is>
           <t>RespName</t>
         </is>
       </c>
-      <c r="E92" s="101" t="inlineStr">
+      <c r="E92" s="100" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="H92" s="101" t="inlineStr">
+      <c r="H92" s="100" t="inlineStr">
         <is>
           <t>Respondent name</t>
         </is>
       </c>
-      <c r="I92" s="101" t="inlineStr">
+      <c r="I92" s="100" t="inlineStr">
         <is>
           <t>[INJECTED_DATA.TestField]="TTT"</t>
         </is>
       </c>
-      <c r="M92" s="101" t="inlineStr">
+      <c r="M92" s="100" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="100" t="n">
+      <c r="A93" s="99" t="n">
         <v>42745</v>
       </c>
-      <c r="C93" s="101" t="inlineStr">
+      <c r="C93" s="100" t="inlineStr">
         <is>
           <t>RespondentComplex6</t>
         </is>
       </c>
-      <c r="D93" s="101" t="inlineStr">
+      <c r="D93" s="100" t="inlineStr">
         <is>
           <t>RespAddress4</t>
         </is>
       </c>
-      <c r="E93" s="101" t="inlineStr">
+      <c r="E93" s="100" t="inlineStr">
         <is>
           <t>AddressUK</t>
         </is>
       </c>
-      <c r="H93" s="101" t="inlineStr">
+      <c r="H93" s="100" t="inlineStr">
         <is>
           <t>Respondent address 4</t>
         </is>
       </c>
-      <c r="M93" s="101" t="inlineStr">
+      <c r="M93" s="100" t="inlineStr">
         <is>
           <t>PUBLIC</t>
         </is>
@@ -21015,7 +18568,7 @@
           <t>IndividualLastName</t>
         </is>
       </c>
-      <c r="E95" s="104" t="inlineStr">
+      <c r="E95" s="103" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -21075,7 +18628,7 @@
           <t>IndividualAddress</t>
         </is>
       </c>
-      <c r="E97" s="104" t="inlineStr">
+      <c r="E97" s="103" t="inlineStr">
         <is>
           <t>AddressUK</t>
         </is>
@@ -21342,278 +18895,278 @@
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="105" t="n">
+      <c r="A106" s="104" t="n">
         <v>42737</v>
       </c>
-      <c r="C106" s="106" t="inlineStr">
+      <c r="C106" s="105" t="inlineStr">
         <is>
           <t>ProofType</t>
         </is>
       </c>
-      <c r="D106" s="106" t="inlineStr">
+      <c r="D106" s="105" t="inlineStr">
         <is>
           <t>typeOfProof</t>
         </is>
       </c>
-      <c r="E106" s="106" t="inlineStr">
+      <c r="E106" s="105" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="H106" s="106" t="inlineStr">
+      <c r="H106" s="105" t="inlineStr">
         <is>
           <t>Proof Type</t>
         </is>
       </c>
-      <c r="M106" s="106" t="inlineStr">
+      <c r="M106" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="105" t="n">
+      <c r="A107" s="104" t="n">
         <v>42738</v>
       </c>
-      <c r="C107" s="106" t="inlineStr">
+      <c r="C107" s="105" t="inlineStr">
         <is>
           <t>ProofType</t>
         </is>
       </c>
-      <c r="D107" s="106" t="inlineStr">
+      <c r="D107" s="105" t="inlineStr">
         <is>
           <t>dateIssued</t>
         </is>
       </c>
-      <c r="E107" s="106" t="inlineStr">
+      <c r="E107" s="105" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="H107" s="106" t="inlineStr">
+      <c r="H107" s="105" t="inlineStr">
         <is>
           <t>Date of Issue</t>
         </is>
       </c>
-      <c r="M107" s="106" t="inlineStr">
+      <c r="M107" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="105" t="n">
+      <c r="A108" s="104" t="n">
         <v>42739</v>
       </c>
-      <c r="C108" s="106" t="inlineStr">
+      <c r="C108" s="105" t="inlineStr">
         <is>
           <t>ProofType</t>
         </is>
       </c>
-      <c r="D108" s="106" t="inlineStr">
+      <c r="D108" s="105" t="inlineStr">
         <is>
           <t>documentEvidence</t>
         </is>
       </c>
-      <c r="E108" s="106" t="inlineStr">
+      <c r="E108" s="105" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="F108" s="106" t="n"/>
-      <c r="H108" s="106" t="inlineStr">
+      <c r="F108" s="105" t="n"/>
+      <c r="H108" s="105" t="inlineStr">
         <is>
           <t>Attach Document</t>
         </is>
       </c>
-      <c r="M108" s="106" t="inlineStr">
+      <c r="M108" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="105" t="n">
+      <c r="A109" s="104" t="n">
         <v>42739</v>
       </c>
-      <c r="C109" s="106" t="inlineStr">
+      <c r="C109" s="105" t="inlineStr">
         <is>
           <t>ProofType</t>
         </is>
       </c>
-      <c r="D109" s="106" t="inlineStr">
+      <c r="D109" s="105" t="inlineStr">
         <is>
           <t>documentEvidenceCollection</t>
         </is>
       </c>
-      <c r="E109" s="106" t="inlineStr">
+      <c r="E109" s="105" t="inlineStr">
         <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="F109" s="106" t="n"/>
+      <c r="F109" s="105" t="n"/>
       <c r="G109" s="90" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="H109" s="106" t="inlineStr">
+      <c r="H109" s="105" t="inlineStr">
         <is>
           <t>Attach Document Collection</t>
         </is>
       </c>
-      <c r="M109" s="106" t="inlineStr">
+      <c r="M109" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="105" t="n">
+      <c r="A110" s="104" t="n">
         <v>42740</v>
       </c>
-      <c r="C110" s="106" t="inlineStr">
+      <c r="C110" s="105" t="inlineStr">
         <is>
           <t>documentWithMetadata</t>
         </is>
       </c>
-      <c r="D110" s="106" t="inlineStr">
+      <c r="D110" s="105" t="inlineStr">
         <is>
           <t>issuedBy</t>
         </is>
       </c>
-      <c r="E110" s="106" t="inlineStr">
+      <c r="E110" s="105" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="H110" s="106" t="inlineStr">
+      <c r="H110" s="105" t="inlineStr">
         <is>
           <t>Issued By</t>
         </is>
       </c>
-      <c r="M110" s="106" t="inlineStr">
+      <c r="M110" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="105" t="n">
+      <c r="A111" s="104" t="n">
         <v>42741</v>
       </c>
-      <c r="C111" s="106" t="inlineStr">
+      <c r="C111" s="105" t="inlineStr">
         <is>
           <t>documentWithMetadata</t>
         </is>
       </c>
-      <c r="D111" s="106" t="inlineStr">
+      <c r="D111" s="105" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E111" s="106" t="inlineStr">
+      <c r="E111" s="105" t="inlineStr">
         <is>
           <t>TextArea</t>
         </is>
       </c>
-      <c r="H111" s="106" t="inlineStr">
+      <c r="H111" s="105" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="M111" s="106" t="inlineStr">
+      <c r="M111" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="105" t="n">
+      <c r="A112" s="104" t="n">
         <v>42742</v>
       </c>
-      <c r="C112" s="106" t="inlineStr">
+      <c r="C112" s="105" t="inlineStr">
         <is>
           <t>documentWithMetadata</t>
         </is>
       </c>
-      <c r="D112" s="106" t="inlineStr">
+      <c r="D112" s="105" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="E112" s="106" t="inlineStr">
+      <c r="E112" s="105" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="F112" s="106" t="n"/>
-      <c r="H112" s="106" t="inlineStr">
+      <c r="F112" s="105" t="n"/>
+      <c r="H112" s="105" t="inlineStr">
         <is>
           <t>Upload file</t>
         </is>
       </c>
-      <c r="M112" s="106" t="inlineStr">
+      <c r="M112" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="105" t="n">
+      <c r="A113" s="104" t="n">
         <v>42742</v>
       </c>
-      <c r="C113" s="106" t="inlineStr">
+      <c r="C113" s="105" t="inlineStr">
         <is>
           <t>nextHearingDetails</t>
         </is>
       </c>
-      <c r="D113" s="106" t="inlineStr">
+      <c r="D113" s="105" t="inlineStr">
         <is>
           <t>hearingID</t>
         </is>
       </c>
-      <c r="E113" s="106" t="inlineStr">
+      <c r="E113" s="105" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="H113" s="106" t="inlineStr">
+      <c r="H113" s="105" t="inlineStr">
         <is>
           <t>Hearing Id</t>
         </is>
       </c>
-      <c r="M113" s="106" t="inlineStr">
+      <c r="M113" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="105" t="n">
+      <c r="A114" s="104" t="n">
         <v>42742</v>
       </c>
-      <c r="C114" s="106" t="inlineStr">
+      <c r="C114" s="105" t="inlineStr">
         <is>
           <t>nextHearingDetails</t>
         </is>
       </c>
-      <c r="D114" s="106" t="inlineStr">
+      <c r="D114" s="105" t="inlineStr">
         <is>
           <t>hearingDateTime</t>
         </is>
       </c>
-      <c r="E114" s="106" t="inlineStr">
+      <c r="E114" s="105" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="H114" s="106" t="inlineStr">
+      <c r="H114" s="105" t="inlineStr">
         <is>
           <t>Hearing Date</t>
         </is>
       </c>
-      <c r="M114" s="106" t="inlineStr">
+      <c r="M114" s="105" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
@@ -21634,7 +19187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="23.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -21779,7 +19332,7 @@
     <row r="4" ht="20" customFormat="1" customHeight="1" s="37">
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
@@ -21824,7 +19377,7 @@
     <row r="5" ht="20" customFormat="1" customHeight="1" s="37">
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
@@ -21869,7 +19422,7 @@
     <row r="6" ht="20" customFormat="1" customHeight="1" s="37">
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
@@ -21906,141 +19459,6 @@
         </is>
       </c>
       <c r="J6" s="85" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>NoCChallenge</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t>What's the name of the party you wish to represent?</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G7" s="37" t="inlineStr">
-        <is>
-          <t>#DATETIMEENTRY(dd-MM-yyyy)</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>${OrganisationField.OrganisationName}|${OrganisationField.OrganisationID}:[Claimant],${OrganisationField.OrganisationName}|${OrganisationField.OrganisationID}:[Defendant]</t>
-        </is>
-      </c>
-      <c r="I7" s="37" t="inlineStr">
-        <is>
-          <t>NoCChallengeQ1</t>
-        </is>
-      </c>
-      <c r="J7" s="85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>NoCChallenge</t>
-        </is>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>What's xxxx?</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="inlineStr">
-        <is>
-          <t>#DATETIMEENTRY(dd-MM-yyyy)</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>${OrganisationField.OrganisationName}|${OrganisationField.OrganisationID}:[Defendant]</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>NoCChallengeQ2</t>
-        </is>
-      </c>
-      <c r="J8" s="89" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>NoCChallenge</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>What  time is it?</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
-        <is>
-          <t>#DATETIMEENTRY(dd-MM-yyyy)</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>${OrganisationField.OrganisationID}:[Defendant]</t>
-        </is>
-      </c>
-      <c r="I9" s="37" t="inlineStr">
-        <is>
-          <t>NoCChallengeQ3</t>
-        </is>
-      </c>
-      <c r="J9" s="85" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -22068,7 +19486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="16.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -22240,7 +19658,7 @@
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D4" s="37" t="inlineStr">
@@ -22276,7 +19694,7 @@
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -22312,7 +19730,7 @@
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
@@ -22348,7 +19766,7 @@
       </c>
       <c r="C7" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
@@ -22384,7 +19802,7 @@
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>FT_CaseAccessGroups</t>
+          <t>FT_CaseProfessionalGroupAccess</t>
         </is>
       </c>
       <c r="D8" s="37" t="inlineStr">
@@ -22414,189 +19832,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>notApplicable</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="37" t="inlineStr">
-        <is>
-          <t>CaseAccessGroups</t>
-        </is>
-      </c>
-      <c r="I9" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A10" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>notApplicable</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationField</t>
-        </is>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A11" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C11" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>notApplicable</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicy</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Organisation Policy</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>OrganisationPolicyField</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A12" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>notApplicable</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequest</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>Change Organisation Request</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>ChangeOrganisationRequestField</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customFormat="1" customHeight="1" s="37">
-      <c r="A13" s="35" t="n">
-        <v>42736</v>
-      </c>
-      <c r="C13" s="37" t="inlineStr">
-        <is>
-          <t>FT_CaseAccessGroups_Align_Befta</t>
-        </is>
-      </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>notApplicable</t>
-        </is>
-      </c>
-      <c r="E13" s="37" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="37" t="inlineStr">
-        <is>
-          <t>CaseHistory</t>
-        </is>
-      </c>
-      <c r="I13" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G58:G68 G90 I58:I68 I90" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G53:G63 G85 I53:I63 I85" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a number greater than 0" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/BEFTA_MASTER_GROUPACCESS.xlsx
+++ b/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/BEFTA_MASTER_GROUPACCESS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilapatel/Documents/Work/repos/ccd-test-definitions/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B154CB-DADC-684F-814D-35C54D6B752A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EC3DE6-B33D-B648-8BF1-363C0AB33D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39280" yWindow="2280" windowWidth="30200" windowHeight="16620" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39280" yWindow="2280" windowWidth="30200" windowHeight="16620" firstSheet="18" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jurisdiction" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="647">
   <si>
     <t>Jurisdiction</t>
   </si>
@@ -4013,6 +4013,45 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -4023,6 +4062,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4044,6 +4084,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4055,16 +4096,15 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4076,16 +4116,15 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4128,7 +4167,8 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -4140,70 +4180,42 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -4230,6 +4242,25 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
@@ -4250,7 +4281,6 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4358,26 +4388,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -4388,6 +4398,95 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4399,6 +4498,8 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -4411,26 +4512,51 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4450,7 +4576,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4490,14 +4616,12 @@
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
@@ -4514,9 +4638,9 @@
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0432FF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4534,6 +4658,18 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -4544,13 +4680,25 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -4570,7 +4718,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4588,11 +4736,11 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4614,9 +4762,21 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -4632,97 +4792,11 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4757,36 +4831,33 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0432FF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4808,9 +4879,35 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -4830,21 +4927,9 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -4864,7 +4949,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4886,7 +4971,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4908,21 +4993,9 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -4938,11 +5011,55 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -4977,9 +5094,16 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -5021,44 +5145,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -5069,13 +5155,45 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -5091,14 +5209,108 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5109,7 +5321,7 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
+        <color theme="0"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -5121,6 +5333,16 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5157,7 +5379,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -5179,7 +5401,91 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -5236,6 +5542,8 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -5291,6 +5599,179 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -5301,45 +5782,71 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -5355,108 +5862,14 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
@@ -5467,7 +5880,7 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -5475,20 +5888,10 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
@@ -5507,7 +5910,27 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -5525,11 +5948,31 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -5551,78 +5994,14 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -5635,16 +6014,14 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -5657,7 +6034,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -5688,20 +6065,19 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -5716,6 +6092,8 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -5724,6 +6102,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -5754,107 +6133,6 @@
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -5869,44 +6147,6 @@
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -5928,7 +6168,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -5986,6 +6226,46 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill>
@@ -5993,7 +6273,107 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -6020,8 +6400,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -6042,8 +6420,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -6072,7 +6448,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -6084,8 +6460,26 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -6220,12 +6614,6 @@
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -6274,21 +6662,80 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -6296,7 +6743,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -6310,7 +6757,7 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
+        <color indexed="8"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -6318,381 +6765,18 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -6700,19 +6784,18 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -6720,7 +6803,7 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -6755,11 +6838,16 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -6808,6 +6896,7 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -6826,13 +6915,12 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6845,12 +6933,12 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6863,13 +6951,12 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6882,13 +6969,12 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6897,20 +6983,16 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6923,13 +7005,12 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6942,13 +7023,84 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -6984,13 +7136,13 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
-          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -7046,6 +7198,160 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -7053,201 +7359,312 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7286,10 +7703,10 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7303,6 +7720,7 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
@@ -7314,11 +7732,10 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0432FF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7344,145 +7761,33 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
@@ -7493,7 +7798,7 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -7502,92 +7807,6 @@
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7605,192 +7824,47 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7809,8 +7883,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <fill>
         <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7851,8 +7924,7 @@
       </font>
       <fill>
         <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7879,9 +7951,9 @@
         <family val="2"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0432FF"/>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -7927,6 +7999,183 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -7948,7 +8197,6 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -7973,7 +8221,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
-          <fgColor rgb="FF000000"/>
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -7982,16 +8230,20 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -8000,16 +8252,20 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -8026,9 +8282,30 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill>
+      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -8068,8 +8345,10 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -8084,7 +8363,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
@@ -8092,10 +8370,11 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -8165,7 +8444,6 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -8185,7 +8463,6 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -8243,7 +8520,6 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -8301,27 +8577,6 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -8333,122 +8588,14 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;DD/&quot;mm&quot;/YYYY&quot;"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -8516,7 +8663,7 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color indexed="8"/>
+        <color theme="0"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
@@ -8542,210 +8689,83 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center"/>
@@ -8784,14 +8804,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -8803,8 +8816,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
@@ -8813,24 +8824,13 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <fill>
@@ -9030,218 +9030,218 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Table9" displayName="Table9" ref="A3:H5" totalsRowShown="0" headerRowDxfId="231" dataDxfId="229" headerRowBorderDxfId="230" tableBorderDxfId="228" totalsRowBorderDxfId="227">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Table9" displayName="Table9" ref="A3:H5" totalsRowShown="0" headerRowDxfId="222" dataDxfId="220" headerRowBorderDxfId="221" tableBorderDxfId="219" totalsRowBorderDxfId="218">
   <autoFilter ref="A3:H5" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="LiveFrom" dataDxfId="226"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="LiveTo" dataDxfId="225"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="CaseTypeID" dataDxfId="224"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="ID" dataDxfId="223"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Name" dataDxfId="222"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="Description" dataDxfId="221"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="DisplayOrder" dataDxfId="220"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="TitleDisplay" dataDxfId="219"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="LiveFrom" dataDxfId="217"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="LiveTo" dataDxfId="216"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="CaseTypeID" dataDxfId="215"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="ID" dataDxfId="214"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Name" dataDxfId="213"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="Description" dataDxfId="212"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="DisplayOrder" dataDxfId="211"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="TitleDisplay" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Table10" displayName="Table10" ref="A3:W7" totalsRowShown="0" headerRowDxfId="218" dataDxfId="216" headerRowBorderDxfId="217" tableBorderDxfId="215" totalsRowBorderDxfId="214">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Table10" displayName="Table10" ref="A3:W7" totalsRowShown="0" headerRowDxfId="209" dataDxfId="207" headerRowBorderDxfId="208" tableBorderDxfId="206" totalsRowBorderDxfId="205">
   <autoFilter ref="A3:W7" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="LiveFrom" dataDxfId="213"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="LiveTo" dataDxfId="212"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="CaseTypeID" dataDxfId="211"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="ID" dataDxfId="210"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="Name" dataDxfId="209"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="Description" dataDxfId="208"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="DisplayOrder" dataDxfId="207"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="PreConditionState(s)" dataDxfId="206"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="PostConditionState" dataDxfId="205"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0B00-000016000000}" name="EventEnablingCondition" dataDxfId="204"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="CallBackURLAboutToStartEvent" dataDxfId="203"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="RetriesTimeoutAboutToStartEvent" dataDxfId="202"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0B00-00000C000000}" name="CallBackURLAboutToSubmitEvent" dataDxfId="201"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0B00-00000D000000}" name="RetriesTimeoutURLAboutToSubmitEvent" dataDxfId="200"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0B00-00000E000000}" name="CallBackURLSubmittedEvent" dataDxfId="199"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0B00-00000F000000}" name="RetriesTimeoutURLSubmittedEvent" dataDxfId="198"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0B00-000010000000}" name="SecurityClassification" dataDxfId="197"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0B00-000011000000}" name="ShowSummary" dataDxfId="196"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0B00-000012000000}" name="ShowEventNotes" dataDxfId="195"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0B00-000013000000}" name="CanSaveDraft" dataDxfId="194"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0B00-000015000000}" name="EndButtonLabel" dataDxfId="193"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0B00-000014000000}" name="Publish" dataDxfId="192"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0B00-000017000000}" name="TTLIncrement" dataDxfId="191"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="LiveFrom" dataDxfId="204"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="LiveTo" dataDxfId="203"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="CaseTypeID" dataDxfId="202"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="ID" dataDxfId="201"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="Name" dataDxfId="200"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="Description" dataDxfId="199"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="DisplayOrder" dataDxfId="198"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="PreConditionState(s)" dataDxfId="197"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="PostConditionState" dataDxfId="196"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0B00-000016000000}" name="EventEnablingCondition" dataDxfId="195"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="CallBackURLAboutToStartEvent" dataDxfId="194"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="RetriesTimeoutAboutToStartEvent" dataDxfId="193"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0B00-00000C000000}" name="CallBackURLAboutToSubmitEvent" dataDxfId="192"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0B00-00000D000000}" name="RetriesTimeoutURLAboutToSubmitEvent" dataDxfId="191"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0B00-00000E000000}" name="CallBackURLSubmittedEvent" dataDxfId="190"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0B00-00000F000000}" name="RetriesTimeoutURLSubmittedEvent" dataDxfId="189"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0B00-000010000000}" name="SecurityClassification" dataDxfId="188"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0B00-000011000000}" name="ShowSummary" dataDxfId="187"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0B00-000012000000}" name="ShowEventNotes" dataDxfId="186"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0B00-000013000000}" name="CanSaveDraft" dataDxfId="185"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0B00-000015000000}" name="EndButtonLabel" dataDxfId="184"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0B00-000014000000}" name="Publish" dataDxfId="183"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0B00-000017000000}" name="TTLIncrement" dataDxfId="182"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Table11" displayName="Table11" ref="A3:V7" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187" totalsRowBorderDxfId="186">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Table11" displayName="Table11" ref="A3:V7" totalsRowShown="0" headerRowDxfId="181" dataDxfId="179" headerRowBorderDxfId="180" tableBorderDxfId="178" totalsRowBorderDxfId="177">
   <autoFilter ref="A3:V7" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="LiveFrom" dataDxfId="185"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="LiveTo" dataDxfId="184"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="CaseTypeID" dataDxfId="183"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="CaseEventID" dataDxfId="182"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="CaseFieldID" dataDxfId="181"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="PageFieldDisplayOrder" dataDxfId="180"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0C00-000007000000}" name="DisplayContext" dataDxfId="179"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0C00-000008000000}" name="PageID" dataDxfId="178"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0C00-000009000000}" name="PageLabel" dataDxfId="177"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0C00-00000A000000}" name="PageDisplayOrder" dataDxfId="176"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0C00-00000B000000}" name="PageColumnNumber" dataDxfId="175"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0C00-00000C000000}" name="FieldShowCondition" dataDxfId="174"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0C00-000012000000}" name="RetainHiddenValue" dataDxfId="173"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0C00-00000D000000}" name="PageShowCondition" dataDxfId="172"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0C00-00000E000000}" name="DisplayContextParameter" dataDxfId="171"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0C00-00000F000000}" name="ShowSummaryChangeOption" dataDxfId="170"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0C00-000010000000}" name="ShowSummaryContentOption" dataDxfId="169"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0C00-000011000000}" name="CallBackURLMidEvent" dataDxfId="168"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0C00-000013000000}" name="Publish" dataDxfId="167"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0C00-000014000000}" name="PublishAs" dataDxfId="166"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0C00-000015000000}" name="DefaultValue" dataDxfId="165"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0C00-000016000000}" name="NullifyByDefault" dataDxfId="164"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="LiveFrom" dataDxfId="176"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="LiveTo" dataDxfId="175"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="CaseTypeID" dataDxfId="174"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="CaseEventID" dataDxfId="173"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="CaseFieldID" dataDxfId="172"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="PageFieldDisplayOrder" dataDxfId="171"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0C00-000007000000}" name="DisplayContext" dataDxfId="170"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0C00-000008000000}" name="PageID" dataDxfId="169"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0C00-000009000000}" name="PageLabel" dataDxfId="168"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0C00-00000A000000}" name="PageDisplayOrder" dataDxfId="167"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0C00-00000B000000}" name="PageColumnNumber" dataDxfId="166"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0C00-00000C000000}" name="FieldShowCondition" dataDxfId="165"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0C00-000012000000}" name="RetainHiddenValue" dataDxfId="164"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0C00-00000D000000}" name="PageShowCondition" dataDxfId="163"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0C00-00000E000000}" name="DisplayContextParameter" dataDxfId="162"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0C00-00000F000000}" name="ShowSummaryChangeOption" dataDxfId="161"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0C00-000010000000}" name="ShowSummaryContentOption" dataDxfId="160"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0C00-000011000000}" name="CallBackURLMidEvent" dataDxfId="159"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0C00-000013000000}" name="Publish" dataDxfId="158"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0C00-000014000000}" name="PublishAs" dataDxfId="157"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0C00-000015000000}" name="DefaultValue" dataDxfId="156"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0C00-000016000000}" name="NullifyByDefault" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Table12" displayName="Table12" ref="A3:H7" totalsRowShown="0" headerRowDxfId="163" dataDxfId="161" headerRowBorderDxfId="162" tableBorderDxfId="160" totalsRowBorderDxfId="159">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Table12" displayName="Table12" ref="A3:H7" totalsRowShown="0" headerRowDxfId="154" dataDxfId="152" headerRowBorderDxfId="153" tableBorderDxfId="151" totalsRowBorderDxfId="150">
   <autoFilter ref="A3:H7" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="LiveFrom" dataDxfId="158"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="LiveTo" dataDxfId="157"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="CaseTypeID" dataDxfId="156"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="CaseFieldID" dataDxfId="155"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="ListElementCode" dataDxfId="154"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="Label" dataDxfId="153"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="DisplayOrder" dataDxfId="152"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0D00-000008000000}" name="DisplayContextParameter" dataDxfId="151"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="LiveFrom" dataDxfId="149"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="LiveTo" dataDxfId="148"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="CaseTypeID" dataDxfId="147"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="CaseFieldID" dataDxfId="146"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="ListElementCode" dataDxfId="145"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="Label" dataDxfId="144"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="DisplayOrder" dataDxfId="143"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0D00-000008000000}" name="DisplayContextParameter" dataDxfId="142"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Table25" displayName="Table25" ref="A3:K5" totalsRowShown="0" headerRowDxfId="150" dataDxfId="148" headerRowBorderDxfId="149">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Table25" displayName="Table25" ref="A3:K5" totalsRowShown="0" headerRowDxfId="141" dataDxfId="139" headerRowBorderDxfId="140">
   <autoFilter ref="A3:K5" xr:uid="{00000000-0009-0000-0100-00000F000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="LiveFrom" dataDxfId="147" dataCellStyle="Normal 3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="LiveTo" dataDxfId="146" dataCellStyle="Normal 3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="CaseTypeID" dataDxfId="145" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="AccessProfile" dataDxfId="144"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0E00-000005000000}" name="CaseFieldID" dataDxfId="143" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0E00-000006000000}" name="ListElementCode" dataDxfId="142" dataCellStyle="Normal 3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0E00-000007000000}" name="Label" dataDxfId="141" dataCellStyle="Normal 3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0E00-000008000000}" name="DisplayOrder" dataDxfId="140" dataCellStyle="Normal 3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0E00-000009000000}" name="ResultsOrdering" dataDxfId="139"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0E00-00000A000000}" name="DisplayContextParameter" dataDxfId="138" dataCellStyle="Normal 3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0E00-00000B000000}" name="UseCase" dataDxfId="137" dataCellStyle="Normal 3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="LiveFrom" dataDxfId="138" dataCellStyle="Normal 3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="LiveTo" dataDxfId="137" dataCellStyle="Normal 3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="CaseTypeID" dataDxfId="136" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="AccessProfile" dataDxfId="135"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0E00-000005000000}" name="CaseFieldID" dataDxfId="134" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0E00-000006000000}" name="ListElementCode" dataDxfId="133" dataCellStyle="Normal 3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0E00-000007000000}" name="Label" dataDxfId="132" dataCellStyle="Normal 3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0E00-000008000000}" name="DisplayOrder" dataDxfId="131" dataCellStyle="Normal 3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0E00-000009000000}" name="ResultsOrdering" dataDxfId="130"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0E00-00000A000000}" name="DisplayContextParameter" dataDxfId="129" dataCellStyle="Normal 3"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0E00-00000B000000}" name="UseCase" dataDxfId="128" dataCellStyle="Normal 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Table14" displayName="Table14" ref="A3:I6" totalsRowShown="0" headerRowDxfId="136" dataDxfId="134" headerRowBorderDxfId="135" tableBorderDxfId="133" totalsRowBorderDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Table14" displayName="Table14" ref="A3:I6" totalsRowShown="0" headerRowDxfId="127" dataDxfId="125" headerRowBorderDxfId="126" tableBorderDxfId="124" totalsRowBorderDxfId="123">
   <autoFilter ref="A3:I6" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="LiveFrom" dataDxfId="131"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="LiveTo" dataDxfId="130"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="CaseTypeID" dataDxfId="129"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="CaseFieldID" dataDxfId="128"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="Label" dataDxfId="127"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="ListElementCode" dataDxfId="126"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="DisplayOrder" dataDxfId="125"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="ResultsOrdering" dataDxfId="124"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="DisplayContextParameter" dataDxfId="123"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="LiveFrom" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="LiveTo" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="CaseTypeID" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="CaseFieldID" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="Label" dataDxfId="118"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="ListElementCode" dataDxfId="117"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="DisplayOrder" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="ResultsOrdering" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="DisplayContextParameter" dataDxfId="114"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table15" displayName="Table15" ref="A3:H7" totalsRowShown="0" headerRowDxfId="122" dataDxfId="120" headerRowBorderDxfId="121" tableBorderDxfId="119" totalsRowBorderDxfId="118">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table15" displayName="Table15" ref="A3:H7" totalsRowShown="0" headerRowDxfId="113" dataDxfId="111" headerRowBorderDxfId="112" tableBorderDxfId="110" totalsRowBorderDxfId="109">
   <autoFilter ref="A3:H7" xr:uid="{00000000-0009-0000-0100-000011000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="LiveFrom" dataDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="LiveTo" dataDxfId="116"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="CaseTypeID" dataDxfId="115"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="CaseFieldID" dataDxfId="114"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="ListElementCode" dataDxfId="113"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Label" dataDxfId="112"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="DisplayOrder" dataDxfId="111"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="DisplayContextParameter" dataDxfId="110"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="LiveFrom" dataDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="LiveTo" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="CaseTypeID" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="CaseFieldID" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="ListElementCode" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Label" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="DisplayOrder" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="DisplayContextParameter" dataDxfId="101"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Table16" displayName="Table16" ref="A3:I6" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108" tableBorderDxfId="107" totalsRowBorderDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Table16" displayName="Table16" ref="A3:I6" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99" tableBorderDxfId="98" totalsRowBorderDxfId="97">
   <autoFilter ref="A3:I6" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="LiveFrom" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="LiveTo" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="CaseTypeID" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="CaseFieldID" dataDxfId="102"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="ListElementCode" dataDxfId="101"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="Label" dataDxfId="100"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="DisplayOrder" dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="ResultsOrdering" dataDxfId="98"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="DisplayContextParameter" dataDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="LiveFrom" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="LiveTo" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="CaseTypeID" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="CaseFieldID" dataDxfId="93"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="ListElementCode" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="Label" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="DisplayOrder" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="ResultsOrdering" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="DisplayContextParameter" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{00000000-000C-0000-FFFF-FFFF12000000}" name="Table18" displayName="Table18" ref="A3:E6" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{00000000-000C-0000-FFFF-FFFF12000000}" name="Table18" displayName="Table18" ref="A3:E6" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" totalsRowBorderDxfId="83">
   <autoFilter ref="A3:E6" xr:uid="{00000000-0009-0000-0100-000013000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1200-000001000000}" name="LiveFrom" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1200-000002000000}" name="LiveTo" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1200-000003000000}" name="CaseTypeID" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1200-000004000000}" name="UserRole" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1200-000005000000}" name="CRUD" dataDxfId="87"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1200-000001000000}" name="LiveFrom" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1200-000002000000}" name="LiveTo" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1200-000003000000}" name="CaseTypeID" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1200-000004000000}" name="UserRole" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1200-000005000000}" name="CRUD" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3" displayName="Table3" ref="A3:K4" totalsRowShown="0" headerRowDxfId="331" dataDxfId="329" headerRowBorderDxfId="330" tableBorderDxfId="328" totalsRowBorderDxfId="327">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3" displayName="Table3" ref="A3:K4" totalsRowShown="0" headerRowDxfId="322" dataDxfId="320" headerRowBorderDxfId="321" tableBorderDxfId="319" totalsRowBorderDxfId="318">
   <autoFilter ref="A3:K4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="LiveFrom" dataDxfId="326"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="LiveTo" dataDxfId="325"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="ID" dataDxfId="324"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Name" dataDxfId="323"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description" dataDxfId="322"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="JurisdictionID" dataDxfId="321"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="PrintableDocumentsUrl" dataDxfId="320"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="RetriesTimeoutURLPrintEvent" dataDxfId="319"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="SecurityClassification" dataDxfId="318"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CallbackGetCaseUrl" dataDxfId="317"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="RetriesGetCaseUrl" dataDxfId="316"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="LiveFrom" dataDxfId="317"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="LiveTo" dataDxfId="316"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="ID" dataDxfId="315"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Name" dataDxfId="314"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description" dataDxfId="313"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="JurisdictionID" dataDxfId="312"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="PrintableDocumentsUrl" dataDxfId="311"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="RetriesTimeoutURLPrintEvent" dataDxfId="310"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="SecurityClassification" dataDxfId="309"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CallbackGetCaseUrl" dataDxfId="308"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="RetriesGetCaseUrl" dataDxfId="307"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF13000000}" name="Table19" displayName="Table19" ref="A3:F15" totalsRowShown="0" headerRowDxfId="86" dataDxfId="84" headerRowBorderDxfId="85" tableBorderDxfId="83" totalsRowBorderDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF13000000}" name="Table19" displayName="Table19" ref="A3:F15" totalsRowShown="0" headerRowDxfId="77" dataDxfId="75" headerRowBorderDxfId="76" tableBorderDxfId="74" totalsRowBorderDxfId="73">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1300-000001000000}" name="LiveFrom" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1300-000002000000}" name="LiveTo" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1300-000003000000}" name="CaseTypeID" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1300-000004000000}" name="CaseFieldID" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1300-000005000000}" name="UserRole" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1300-000006000000}" name="CRUD" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1300-000001000000}" name="LiveFrom" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1300-000002000000}" name="LiveTo" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1300-000003000000}" name="CaseTypeID" dataDxfId="70"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1300-000004000000}" name="CaseFieldID" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1300-000005000000}" name="UserRole" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1300-000006000000}" name="CRUD" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9263,13 +9263,13 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{00000000-000C-0000-FFFF-FFFF15000000}" name="Table20" displayName="Table20" ref="A3:D5" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72" totalsRowBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{00000000-000C-0000-FFFF-FFFF15000000}" name="Table20" displayName="Table20" ref="A3:D5" totalsRowShown="0" headerRowDxfId="331" dataDxfId="329" headerRowBorderDxfId="330" tableBorderDxfId="328" totalsRowBorderDxfId="327">
   <autoFilter ref="A3:D5" xr:uid="{00000000-0009-0000-0100-000016000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1500-000001000000}" name="CaseTypeID" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1500-000002000000}" name="ID" dataDxfId="69" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1500-000003000000}" name="Name" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1500-000004000000}" name="Description" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1500-000001000000}" name="CaseTypeID" dataDxfId="326"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1500-000002000000}" name="ID" dataDxfId="325" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1500-000003000000}" name="Name" dataDxfId="324"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1500-000004000000}" name="Description" dataDxfId="323"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9363,26 +9363,26 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A3:Q8" totalsRowShown="0" headerRowDxfId="315" dataDxfId="313" headerRowBorderDxfId="314" tableBorderDxfId="312" totalsRowBorderDxfId="311">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A3:Q8" totalsRowShown="0" headerRowDxfId="306" dataDxfId="304" headerRowBorderDxfId="305" tableBorderDxfId="303" totalsRowBorderDxfId="302">
   <autoFilter ref="A3:Q8" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="LiveFrom" dataDxfId="310"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="LiveTo" dataDxfId="309"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="CaseTypeID" dataDxfId="308"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="307"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Label" dataDxfId="306"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="HintText" dataDxfId="305"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="FieldType" dataDxfId="304"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="CategoryID" dataDxfId="303"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="FieldTypeParameter" dataDxfId="302"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="RegularExpression" dataDxfId="301"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="SecurityClassification" dataDxfId="300"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Min" dataDxfId="299"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Max" dataDxfId="298"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="DefaultHidden" dataDxfId="297"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Searchable" dataDxfId="296"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="FieldShowCondition" dataDxfId="295"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="TabShowCondition" dataDxfId="294"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="LiveFrom" dataDxfId="301"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="LiveTo" dataDxfId="300"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="CaseTypeID" dataDxfId="299"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="298"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Label" dataDxfId="297"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="HintText" dataDxfId="296"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="FieldType" dataDxfId="295"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="CategoryID" dataDxfId="294"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="FieldTypeParameter" dataDxfId="293"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="RegularExpression" dataDxfId="292"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="SecurityClassification" dataDxfId="291"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Min" dataDxfId="290"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Max" dataDxfId="289"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="DefaultHidden" dataDxfId="288"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Searchable" dataDxfId="287"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="FieldShowCondition" dataDxfId="286"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="TabShowCondition" dataDxfId="285"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9405,40 +9405,40 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table6" displayName="Table6" ref="A3:G8" totalsRowShown="0" headerRowDxfId="293" dataDxfId="291" headerRowBorderDxfId="292" tableBorderDxfId="290" totalsRowBorderDxfId="289" headerRowCellStyle="Normal 2 3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table6" displayName="Table6" ref="A3:G8" totalsRowShown="0" headerRowDxfId="284" dataDxfId="282" headerRowBorderDxfId="283" tableBorderDxfId="281" totalsRowBorderDxfId="280" headerRowCellStyle="Normal 2 3">
   <autoFilter ref="A3:G8" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="LiveFrom" dataDxfId="288"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="LiveTo" dataDxfId="287"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="CaseTypeID" dataDxfId="286"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="CaseFieldID" dataDxfId="285"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="ListElementCode" dataDxfId="284"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="UserRole" dataDxfId="283"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="CRUD" dataDxfId="282"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="LiveFrom" dataDxfId="279"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="LiveTo" dataDxfId="278"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="CaseTypeID" dataDxfId="277"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="CaseFieldID" dataDxfId="276"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="ListElementCode" dataDxfId="275"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="UserRole" dataDxfId="274"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="CRUD" dataDxfId="273"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table23" displayName="Table23" ref="A3:O5" totalsRowShown="0" headerRowDxfId="281" dataDxfId="279" headerRowBorderDxfId="280" tableBorderDxfId="278" totalsRowBorderDxfId="277">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table23" displayName="Table23" ref="A3:O5" totalsRowShown="0" headerRowDxfId="272" dataDxfId="270" headerRowBorderDxfId="271" tableBorderDxfId="269" totalsRowBorderDxfId="268">
   <autoFilter ref="A3:O5" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="LiveFrom" dataDxfId="276"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="LiveTo" dataDxfId="275"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="ID" dataDxfId="274"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="CaseEventID" dataDxfId="273"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="CaseFieldId" dataDxfId="272"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="ListElementCode" dataDxfId="271"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="DefaultValue" dataDxfId="270"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="EventElementLabel" dataDxfId="269"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="EventHintText" dataDxfId="268"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="FieldDisplayOrder" dataDxfId="267"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="DisplayContext" dataDxfId="266"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="FieldShowCondition" dataDxfId="265"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="RetainHiddenValue" dataDxfId="264"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Publish" dataDxfId="263"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="PublishAs" dataDxfId="262"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="LiveFrom" dataDxfId="267"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="LiveTo" dataDxfId="266"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="ID" dataDxfId="265"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="CaseEventID" dataDxfId="264"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="CaseFieldId" dataDxfId="263"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="ListElementCode" dataDxfId="262"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="DefaultValue" dataDxfId="261"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="EventElementLabel" dataDxfId="260"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="EventHintText" dataDxfId="259"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="FieldDisplayOrder" dataDxfId="258"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="DisplayContext" dataDxfId="257"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="FieldShowCondition" dataDxfId="256"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="RetainHiddenValue" dataDxfId="255"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Publish" dataDxfId="254"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="PublishAs" dataDxfId="253"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9474,40 +9474,40 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table24" displayName="Table24" ref="A3:J6" totalsRowShown="0" headerRowDxfId="261" dataDxfId="259" headerRowBorderDxfId="260">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table24" displayName="Table24" ref="A3:J6" totalsRowShown="0" headerRowDxfId="252" dataDxfId="250" headerRowBorderDxfId="251">
   <autoFilter ref="A3:J6" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="LiveTo" dataDxfId="258"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="CaseTypeID" dataDxfId="257"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ID" dataDxfId="256"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="DisplayOrder" dataDxfId="255"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="QuestionText" dataDxfId="254"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="AnswerFieldType" dataDxfId="253"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="DisplayContextParameter" dataDxfId="252"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Answer" dataDxfId="251"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="QuestionId" dataDxfId="250"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="IgnoreNULLFields" dataDxfId="249"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="LiveTo" dataDxfId="249"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="CaseTypeID" dataDxfId="248"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ID" dataDxfId="247"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="DisplayOrder" dataDxfId="246"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="QuestionText" dataDxfId="245"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="AnswerFieldType" dataDxfId="244"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="DisplayContextParameter" dataDxfId="243"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Answer" dataDxfId="242"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="QuestionId" dataDxfId="241"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="IgnoreNULLFields" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table8" displayName="Table8" ref="A3:L8" totalsRowShown="0" headerRowDxfId="248" dataDxfId="246" headerRowBorderDxfId="247" tableBorderDxfId="245" totalsRowBorderDxfId="244">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table8" displayName="Table8" ref="A3:L8" totalsRowShown="0" headerRowDxfId="239" dataDxfId="237" headerRowBorderDxfId="238" tableBorderDxfId="236" totalsRowBorderDxfId="235">
   <autoFilter ref="A3:L8" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="LiveFrom" dataDxfId="243"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="LiveTo" dataDxfId="242"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="CaseTypeID" dataDxfId="241"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Channel" dataDxfId="240"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="TabID" dataDxfId="239"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="TabLabel" dataDxfId="238"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="TabDisplayOrder" dataDxfId="237"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="CaseFieldID" dataDxfId="236"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="TabFieldDisplayOrder" dataDxfId="235"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="FieldShowCondition" dataDxfId="234"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="TabShowCondition" dataDxfId="233"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="DisplayContextParameter" dataDxfId="232"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="LiveFrom" dataDxfId="234"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="LiveTo" dataDxfId="233"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="CaseTypeID" dataDxfId="232"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Channel" dataDxfId="231"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="TabID" dataDxfId="230"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="TabLabel" dataDxfId="229"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="TabDisplayOrder" dataDxfId="228"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="CaseFieldID" dataDxfId="227"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="TabFieldDisplayOrder" dataDxfId="226"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="FieldShowCondition" dataDxfId="225"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="TabShowCondition" dataDxfId="224"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="DisplayContextParameter" dataDxfId="223"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDefinitionsTab" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14348,9 +14348,7 @@
       <c r="E4" s="36" t="s">
         <v>628</v>
       </c>
-      <c r="F4" s="115" t="s">
-        <v>608</v>
-      </c>
+      <c r="F4" s="115"/>
       <c r="G4" s="36" t="s">
         <v>607</v>
       </c>
@@ -14411,7 +14409,7 @@
       </c>
       <c r="H6" s="36"/>
       <c r="I6" s="37" t="s">
-        <v>540</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/BEFTA_MASTER_GROUPACCESS.xlsx
+++ b/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/BEFTA_MASTER_GROUPACCESS.xlsx
@@ -2018,7 +2018,7 @@
     <t>GA_SOLICITOR</t>
   </si>
   <si>
-    <t>SOLICITOR_PROFILE</t>
+    <t>BEFTA_SOLICITOR_PROFILE</t>
   </si>
   <si>
     <t>BEFTA GA Solicitor Respondent for Org description</t>
@@ -2030,7 +2030,7 @@
     <t>GA_OGD</t>
   </si>
   <si>
-    <t>GOVERNMENT_ORGANISATION_PROFILE</t>
+    <t>BEFTA_GOVERNMENT_ORGANISATION_PROFILE</t>
   </si>
   <si>
     <t>BEFTA GA OGD Respondent for Org description2</t>
